--- a/Python/Activities/data.xlsx
+++ b/Python/Activities/data.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abrig\Documents\Coding_Practice\Python\Activities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{935D91C1-408F-4416-ADF0-9C43BEE8AAAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3954E254-AF62-4E91-AA5F-432F94DF022A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{707279AB-A7E9-4A68-BEA1-90F4DD1BCF34}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$92</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="74">
   <si>
     <t>walk</t>
   </si>
@@ -207,16 +210,55 @@
     <t>12'01"</t>
   </si>
   <si>
-    <t>re</t>
-  </si>
-  <si>
     <t>11'48"</t>
+  </si>
+  <si>
+    <t>13'55"</t>
+  </si>
+  <si>
+    <t>11'17"</t>
+  </si>
+  <si>
+    <t>11'44"</t>
+  </si>
+  <si>
+    <t>11'34"</t>
+  </si>
+  <si>
+    <t>11'11"</t>
+  </si>
+  <si>
+    <t>13'37"</t>
+  </si>
+  <si>
+    <t>10'44"</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Sum</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Running Total</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>11'21"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="hh:mm;@"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -246,10 +288,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -565,78 +609,78 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F196B904-6553-42BC-A222-B01279AC4ED1}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:Q61"/>
+  <dimension ref="A1:Q95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="4" t="s">
         <v>26</v>
       </c>
       <c r="C1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="J1" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>21</v>
       </c>
     </row>
@@ -644,52 +688,52 @@
       <c r="A2" s="1">
         <v>46114</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>0.54097222222222219</v>
       </c>
       <c r="C2" t="s">
         <v>0</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>3789</v>
       </c>
       <c r="E2" t="s">
         <v>22</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>45</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>641</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="3">
         <v>5.05</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6948</v>
       </c>
       <c r="J2" t="s">
         <v>56</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>121</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
+      <c r="L2" s="2">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2">
         <v>56</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>8</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <v>52</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="2">
         <v>2</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="2">
         <v>0</v>
       </c>
     </row>
@@ -697,52 +741,52 @@
       <c r="A3" s="1">
         <v>46122</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>0.55486111111111114</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>4301</v>
       </c>
       <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>71</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>800</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="3">
         <v>5.72</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>7882</v>
       </c>
       <c r="J3" t="s">
         <v>56</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>127</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
+      <c r="L3" s="2">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2">
         <v>73</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>6</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="2">
         <v>47</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="2">
         <v>11</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="2">
         <v>2</v>
       </c>
     </row>
@@ -750,43 +794,43 @@
       <c r="A4" s="1">
         <v>46122</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>0.63611111111111107</v>
       </c>
       <c r="C4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4">
+        <v>68</v>
+      </c>
+      <c r="D4" s="2">
         <v>6403</v>
       </c>
       <c r="E4" t="s">
         <v>22</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>40</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>846</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>108</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
+      <c r="L4" s="2">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2">
         <v>26</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>76</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="2">
         <v>26</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
+      <c r="P4" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2">
         <v>0</v>
       </c>
     </row>
@@ -794,52 +838,52 @@
       <c r="A5" s="1">
         <v>46126</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>0.5625</v>
       </c>
       <c r="C5" t="s">
         <v>0</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>4147</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>46</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>709</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="3">
         <v>5.7</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7846</v>
       </c>
       <c r="J5" t="s">
         <v>52</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>119</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
+      <c r="L5" s="2">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
         <v>58</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>9</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2">
         <v>52</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="2">
         <v>3</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
     </row>
@@ -847,52 +891,52 @@
       <c r="A6" s="1">
         <v>46127</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>0.53472222222222221</v>
       </c>
       <c r="C6" t="s">
         <v>0</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>4250</v>
       </c>
       <c r="E6" t="s">
         <v>22</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>43</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>713</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="3">
         <v>5.82</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8017</v>
       </c>
       <c r="J6" t="s">
         <v>53</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>117</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
+      <c r="L6" s="2">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
         <v>57</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="2">
         <v>12</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="2">
         <v>53</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="2">
         <v>2</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -900,52 +944,52 @@
       <c r="A7" s="1">
         <v>46128</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>0.46388888888888891</v>
       </c>
       <c r="C7" t="s">
         <v>0</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>4250</v>
       </c>
       <c r="E7" t="s">
         <v>22</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>45</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>707</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="3">
         <v>5.76</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7929</v>
       </c>
       <c r="J7" t="s">
         <v>54</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>117</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
+      <c r="L7" s="2">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2">
         <v>60</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="2">
         <v>6</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="2">
         <v>60</v>
       </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
+      <c r="P7" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -953,52 +997,52 @@
       <c r="A8" s="1">
         <v>46129</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>0.55347222222222225</v>
       </c>
       <c r="C8" t="s">
         <v>0</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>7014</v>
       </c>
       <c r="E8" t="s">
         <v>22</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>90</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>1223</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="3">
         <v>9.56</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>13159</v>
       </c>
       <c r="J8" t="s">
         <v>55</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>120</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
+      <c r="L8" s="2">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2">
         <v>115</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="2">
         <v>3</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="2">
         <v>107</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="2">
         <v>4</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1006,46 +1050,46 @@
       <c r="A9" s="1">
         <v>46130</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>0.47361111111111109</v>
       </c>
       <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9">
+        <v>68</v>
+      </c>
+      <c r="D9" s="2">
         <v>2969</v>
       </c>
       <c r="E9" t="s">
         <v>22</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>8</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>293</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="3">
         <v>1.74</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>2400</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>96</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="N9">
+      <c r="L9" s="2">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2">
         <v>44</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
+      <c r="O9" s="2">
+        <v>0</v>
+      </c>
+      <c r="P9" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1053,52 +1097,52 @@
       <c r="A10" s="1">
         <v>46132</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>0.57222222222222219</v>
       </c>
       <c r="C10" t="s">
         <v>0</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>4146</v>
       </c>
       <c r="E10" t="s">
         <v>22</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>50</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>745</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="3">
         <v>6.07</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8026</v>
       </c>
       <c r="J10" t="s">
         <v>48</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>123</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
+      <c r="L10" s="2">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2">
         <v>58</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>4</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>54</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="2">
         <v>2</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1106,52 +1150,52 @@
       <c r="A11" s="1">
         <v>46133</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="4">
         <v>0.54513888888888884</v>
       </c>
       <c r="C11" t="s">
         <v>0</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>4045</v>
       </c>
       <c r="E11" t="s">
         <v>22</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>51</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>719</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="3">
         <v>5.94</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7905</v>
       </c>
       <c r="J11" t="s">
         <v>49</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>122</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
+      <c r="L11" s="2">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2">
         <v>61</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>4</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>61</v>
       </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
+      <c r="P11" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1159,52 +1203,52 @@
       <c r="A12" s="1">
         <v>46134</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="4">
         <v>0.57222222222222219</v>
       </c>
       <c r="C12" t="s">
         <v>0</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>4199</v>
       </c>
       <c r="E12" t="s">
         <v>22</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>61</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>800</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="3">
         <v>5.8</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7993</v>
       </c>
       <c r="J12" t="s">
         <v>50</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>126</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
+      <c r="L12" s="2">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2">
         <v>65</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>2</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="2">
         <v>51</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="2">
         <v>6</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1212,52 +1256,52 @@
       <c r="A13" s="1">
         <v>46135</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="4">
         <v>0.59375</v>
       </c>
       <c r="C13" t="s">
         <v>0</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>4199</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>55</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>775</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="3">
         <v>5.98</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>8144</v>
       </c>
       <c r="J13" t="s">
         <v>51</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>123</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="2">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2">
         <v>60</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>1</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="2">
         <v>60</v>
       </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
+      <c r="P13" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1265,52 +1309,52 @@
       <c r="A14" s="1">
         <v>46139</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>0.55000000000000004</v>
       </c>
       <c r="C14" t="s">
         <v>0</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>4045</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>57</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>745</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="3">
         <v>6</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>7862</v>
       </c>
       <c r="J14" t="s">
         <v>45</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>125</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
+      <c r="L14" s="2">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2">
         <v>68</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>2</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="2">
         <v>54</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="2">
         <v>7</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1318,52 +1362,52 @@
       <c r="A15" s="1">
         <v>46140</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>0.5805555555555556</v>
       </c>
       <c r="C15" t="s">
         <v>0</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>4097</v>
       </c>
       <c r="E15" t="s">
         <v>22</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>52</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>744</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="3">
         <v>5.99</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>7958</v>
       </c>
       <c r="J15" t="s">
         <v>46</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>125</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
+      <c r="L15" s="2">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2">
         <v>58</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>1</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="2">
         <v>56</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="2">
         <v>1</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1371,52 +1415,52 @@
       <c r="A16" s="1">
         <v>46141</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>0.53611111111111109</v>
       </c>
       <c r="C16" t="s">
         <v>0</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>3994</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>63</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>741</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="3">
         <v>6.35</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>7924</v>
       </c>
       <c r="J16" t="s">
         <v>47</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>127</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="2">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2">
         <v>66</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>3</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="2">
         <v>1</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="2">
         <v>1</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="2">
         <v>2</v>
       </c>
     </row>
@@ -1424,52 +1468,52 @@
       <c r="A17" s="1">
         <v>46146</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>0.57361111111111107</v>
       </c>
       <c r="C17" t="s">
         <v>0</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="2">
         <v>3899</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2">
         <v>66</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="2">
         <v>749</v>
       </c>
-      <c r="H17">
+      <c r="H17" s="3">
         <v>6.13</v>
       </c>
-      <c r="I17">
+      <c r="I17" s="2">
         <v>7685</v>
       </c>
       <c r="J17" t="s">
         <v>40</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="2">
         <v>128</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="2">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2">
         <v>75</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
+      <c r="N17" s="2">
+        <v>0</v>
+      </c>
+      <c r="O17" s="2">
         <v>55</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="2">
         <v>10</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1477,52 +1521,52 @@
       <c r="A18" s="1">
         <v>46147</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>0.57499999999999996</v>
       </c>
       <c r="C18" t="s">
         <v>0</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="2">
         <v>4183</v>
       </c>
       <c r="E18" t="s">
         <v>22</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2">
         <v>50</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="2">
         <v>710</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="3">
         <v>5.66</v>
       </c>
-      <c r="I18">
+      <c r="I18" s="2">
         <v>7687</v>
       </c>
       <c r="J18" t="s">
         <v>41</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="2">
         <v>118</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
+      <c r="L18" s="2">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2">
         <v>65</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>4</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="2">
         <v>65</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
+      <c r="P18" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1530,52 +1574,52 @@
       <c r="A19" s="1">
         <v>46148</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>0.44722222222222224</v>
       </c>
       <c r="C19" t="s">
         <v>0</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="2">
         <v>4124</v>
       </c>
       <c r="E19" t="s">
         <v>22</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2">
         <v>53</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="2">
         <v>720</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="3">
         <v>5.9</v>
       </c>
-      <c r="I19">
+      <c r="I19" s="2">
         <v>7778</v>
       </c>
       <c r="J19" t="s">
         <v>42</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="2">
         <v>121</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
+      <c r="L19" s="2">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2">
         <v>71</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
-      <c r="O19">
+      <c r="N19" s="2">
+        <v>0</v>
+      </c>
+      <c r="O19" s="2">
         <v>65</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="2">
         <v>3</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1583,52 +1627,52 @@
       <c r="A20" s="1">
         <v>46149</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>0.57499999999999996</v>
       </c>
       <c r="C20" t="s">
         <v>0</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="2">
         <v>4049</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2">
         <v>60</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="2">
         <v>749</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="3">
         <v>6.16</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="2">
         <v>7886</v>
       </c>
       <c r="J20" t="s">
         <v>43</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>125</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
+      <c r="L20" s="2">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2">
         <v>71</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
+      <c r="N20" s="2">
+        <v>0</v>
+      </c>
+      <c r="O20" s="2">
         <v>65</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="2">
         <v>3</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1636,52 +1680,52 @@
       <c r="A21" s="1">
         <v>46150</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>0.56874999999999998</v>
       </c>
       <c r="C21" t="s">
         <v>0</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="2">
         <v>4046</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2">
         <v>52</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="2">
         <v>741</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="3">
         <v>5.7</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="2">
         <v>7811</v>
       </c>
       <c r="J21" t="s">
         <v>44</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="2">
         <v>126</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
+      <c r="L21" s="2">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2">
         <v>59</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>5</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="2">
         <v>49</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="2">
         <v>5</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1689,52 +1733,52 @@
       <c r="A22" s="1">
         <v>46153</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>0.56666666666666665</v>
       </c>
       <c r="C22" t="s">
         <v>0</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="2">
         <v>4148</v>
       </c>
       <c r="E22" t="s">
         <v>22</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2">
         <v>54</v>
       </c>
-      <c r="G22">
+      <c r="G22" s="2">
         <v>724</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="3">
         <v>5.73</v>
       </c>
-      <c r="I22">
+      <c r="I22" s="2">
         <v>7874</v>
       </c>
       <c r="J22" t="s">
         <v>37</v>
       </c>
-      <c r="K22">
+      <c r="K22" s="2">
         <v>121</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
+      <c r="L22" s="2">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2">
         <v>67</v>
       </c>
-      <c r="N22">
+      <c r="N22" s="2">
         <v>3</v>
       </c>
-      <c r="O22">
+      <c r="O22" s="2">
         <v>63</v>
       </c>
-      <c r="P22">
+      <c r="P22" s="2">
         <v>2</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1742,52 +1786,52 @@
       <c r="A23" s="1">
         <v>46154</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="4">
         <v>0.58611111111111114</v>
       </c>
       <c r="C23" t="s">
         <v>0</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="2">
         <v>3994</v>
       </c>
       <c r="E23" t="s">
         <v>22</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2">
         <v>55</v>
       </c>
-      <c r="G23">
+      <c r="G23" s="2">
         <v>729</v>
       </c>
-      <c r="H23">
+      <c r="H23" s="3">
         <v>6.04</v>
       </c>
-      <c r="I23">
+      <c r="I23" s="2">
         <v>8035</v>
       </c>
       <c r="J23" t="s">
         <v>38</v>
       </c>
-      <c r="K23">
+      <c r="K23" s="2">
         <v>124</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
+      <c r="L23" s="2">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2">
         <v>63</v>
       </c>
-      <c r="N23">
+      <c r="N23" s="2">
         <v>4</v>
       </c>
-      <c r="O23">
+      <c r="O23" s="2">
         <v>61</v>
       </c>
-      <c r="P23">
+      <c r="P23" s="2">
         <v>1</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1795,52 +1839,52 @@
       <c r="A24" s="1">
         <v>46155</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="4">
         <v>0.59097222222222223</v>
       </c>
       <c r="C24" t="s">
         <v>0</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="2">
         <v>4096</v>
       </c>
       <c r="E24" t="s">
         <v>22</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2">
         <v>79</v>
       </c>
-      <c r="G24">
+      <c r="G24" s="2">
         <v>808</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="3">
         <v>5.83</v>
       </c>
-      <c r="I24">
+      <c r="I24" s="2">
         <v>7826</v>
       </c>
       <c r="J24" t="s">
         <v>14</v>
       </c>
-      <c r="K24">
+      <c r="K24" s="2">
         <v>131</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
+      <c r="L24" s="2">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2">
         <v>70</v>
       </c>
-      <c r="N24">
+      <c r="N24" s="2">
         <v>3</v>
       </c>
-      <c r="O24">
+      <c r="O24" s="2">
         <v>38</v>
       </c>
-      <c r="P24">
+      <c r="P24" s="2">
         <v>6</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" s="2">
         <v>10</v>
       </c>
     </row>
@@ -1848,52 +1892,52 @@
       <c r="A25" s="1">
         <v>46157</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="4">
         <v>0.57361111111111107</v>
       </c>
       <c r="C25" t="s">
         <v>0</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="2">
         <v>4097</v>
       </c>
       <c r="E25" t="s">
         <v>22</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2">
         <v>63</v>
       </c>
-      <c r="G25">
+      <c r="G25" s="2">
         <v>755</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="3">
         <v>5.75</v>
       </c>
-      <c r="I25">
+      <c r="I25" s="2">
         <v>7813</v>
       </c>
       <c r="J25" t="s">
         <v>39</v>
       </c>
-      <c r="K25">
+      <c r="K25" s="2">
         <v>127</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
+      <c r="L25" s="2">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2">
         <v>74</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
-      <c r="O25">
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2">
         <v>58</v>
       </c>
-      <c r="P25">
+      <c r="P25" s="2">
         <v>8</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1901,52 +1945,52 @@
       <c r="A26" s="1">
         <v>46161</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="4">
         <v>0.59583333333333333</v>
       </c>
       <c r="C26" t="s">
         <v>0</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="2">
         <v>4094</v>
       </c>
       <c r="E26" t="s">
         <v>22</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2">
         <v>55</v>
       </c>
-      <c r="G26">
+      <c r="G26" s="2">
         <v>724</v>
       </c>
-      <c r="H26">
+      <c r="H26" s="3">
         <v>5.88</v>
       </c>
-      <c r="I26">
+      <c r="I26" s="2">
         <v>7803</v>
       </c>
       <c r="J26" t="s">
         <v>33</v>
       </c>
-      <c r="K26">
+      <c r="K26" s="2">
         <v>122</v>
       </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
+      <c r="L26" s="2">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2">
         <v>67</v>
       </c>
-      <c r="N26">
+      <c r="N26" s="2">
         <v>1</v>
       </c>
-      <c r="O26">
+      <c r="O26" s="2">
         <v>65</v>
       </c>
-      <c r="P26">
+      <c r="P26" s="2">
         <v>1</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" s="2">
         <v>0</v>
       </c>
     </row>
@@ -1954,52 +1998,52 @@
       <c r="A27" s="1">
         <v>46162</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="4">
         <v>0.56180555555555556</v>
       </c>
       <c r="C27" t="s">
         <v>0</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="2">
         <v>2765</v>
       </c>
       <c r="E27" t="s">
         <v>22</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2">
         <v>33</v>
       </c>
-      <c r="G27">
+      <c r="G27" s="2">
         <v>484</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="3">
         <v>3.71</v>
       </c>
-      <c r="I27">
+      <c r="I27" s="2">
         <v>5059</v>
       </c>
       <c r="J27" t="s">
         <v>34</v>
       </c>
-      <c r="K27">
+      <c r="K27" s="2">
         <v>123</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="M27">
+      <c r="L27" s="2">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2">
         <v>39</v>
       </c>
-      <c r="N27">
+      <c r="N27" s="2">
         <v>6</v>
       </c>
-      <c r="O27">
+      <c r="O27" s="2">
         <v>27</v>
       </c>
-      <c r="P27">
+      <c r="P27" s="2">
         <v>6</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2007,52 +2051,52 @@
       <c r="A28" s="1">
         <v>46163</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="4">
         <v>0.60833333333333328</v>
       </c>
       <c r="C28" t="s">
         <v>0</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="2">
         <v>3944</v>
       </c>
       <c r="E28" t="s">
         <v>22</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2">
         <v>49</v>
       </c>
-      <c r="G28">
+      <c r="G28" s="2">
         <v>700</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="3">
         <v>6.14</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="2">
         <v>7576</v>
       </c>
       <c r="J28" t="s">
         <v>35</v>
       </c>
-      <c r="K28">
+      <c r="K28" s="2">
         <v>126</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28">
+      <c r="L28" s="2">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2">
         <v>57</v>
       </c>
-      <c r="N28">
+      <c r="N28" s="2">
         <v>6</v>
       </c>
-      <c r="O28">
+      <c r="O28" s="2">
         <v>47</v>
       </c>
-      <c r="P28">
+      <c r="P28" s="2">
         <v>5</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2060,52 +2104,52 @@
       <c r="A29" s="1">
         <v>46164</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="4">
         <v>0.52847222222222223</v>
       </c>
       <c r="C29" t="s">
         <v>0</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="2">
         <v>3942</v>
       </c>
       <c r="E29" t="s">
         <v>22</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2">
         <v>64</v>
       </c>
-      <c r="G29">
+      <c r="G29" s="2">
         <v>754</v>
       </c>
-      <c r="H29">
+      <c r="H29" s="3">
         <v>5.66</v>
       </c>
-      <c r="I29">
+      <c r="I29" s="2">
         <v>7692</v>
       </c>
       <c r="J29" t="s">
         <v>36</v>
       </c>
-      <c r="K29">
+      <c r="K29" s="2">
         <v>128</v>
       </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
+      <c r="L29" s="2">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2">
         <v>63</v>
       </c>
-      <c r="N29">
+      <c r="N29" s="2">
         <v>2</v>
       </c>
-      <c r="O29">
+      <c r="O29" s="2">
         <v>51</v>
       </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
+      <c r="P29" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2">
         <v>6</v>
       </c>
     </row>
@@ -2113,52 +2157,52 @@
       <c r="A30" s="1">
         <v>46168</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="4">
         <v>0.56458333333333333</v>
       </c>
       <c r="C30" t="s">
         <v>0</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="2">
         <v>4306</v>
       </c>
       <c r="E30" t="s">
         <v>22</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2">
         <v>78</v>
       </c>
-      <c r="G30">
+      <c r="G30" s="2">
         <v>819</v>
       </c>
-      <c r="H30">
+      <c r="H30" s="3">
         <v>5.85</v>
       </c>
-      <c r="I30">
+      <c r="I30" s="2">
         <v>8059</v>
       </c>
       <c r="J30" t="s">
         <v>31</v>
       </c>
-      <c r="K30">
+      <c r="K30" s="2">
         <v>133</v>
       </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
+      <c r="L30" s="2">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2">
         <v>90</v>
       </c>
-      <c r="N30">
+      <c r="N30" s="2">
         <v>3</v>
       </c>
-      <c r="O30">
+      <c r="O30" s="2">
         <v>40</v>
       </c>
-      <c r="P30">
+      <c r="P30" s="2">
         <v>25</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2166,52 +2210,52 @@
       <c r="A31" s="1">
         <v>46169</v>
       </c>
-      <c r="B31" s="2">
+      <c r="B31" s="4">
         <v>0.52777777777777779</v>
       </c>
       <c r="C31" t="s">
         <v>0</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="2">
         <v>3789</v>
       </c>
       <c r="E31" t="s">
         <v>22</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2">
         <v>47</v>
       </c>
-      <c r="G31">
+      <c r="G31" s="2">
         <v>673</v>
       </c>
-      <c r="H31">
+      <c r="H31" s="3">
         <v>5.9</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="2">
         <v>7614</v>
       </c>
       <c r="J31" t="s">
         <v>30</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="2">
         <v>122</v>
       </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
+      <c r="L31" s="2">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2">
         <v>56</v>
       </c>
-      <c r="N31">
+      <c r="N31" s="2">
         <v>4</v>
       </c>
-      <c r="O31">
+      <c r="O31" s="2">
         <v>56</v>
       </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
+      <c r="P31" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2219,52 +2263,52 @@
       <c r="A32" s="1">
         <v>46170</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="4">
         <v>0.58611111111111114</v>
       </c>
       <c r="C32" t="s">
         <v>0</v>
       </c>
-      <c r="D32">
+      <c r="D32" s="2">
         <v>1229</v>
       </c>
       <c r="E32" t="s">
         <v>22</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2">
         <v>17</v>
       </c>
-      <c r="G32">
+      <c r="G32" s="2">
         <v>234</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="3">
         <v>2.2599999999999998</v>
       </c>
-      <c r="I32">
+      <c r="I32" s="2">
         <v>2631</v>
       </c>
       <c r="J32" t="s">
         <v>28</v>
       </c>
-      <c r="K32">
+      <c r="K32" s="2">
         <v>123</v>
       </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
+      <c r="L32" s="2">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2">
         <v>20</v>
       </c>
-      <c r="N32">
+      <c r="N32" s="2">
         <v>3</v>
       </c>
-      <c r="O32">
+      <c r="O32" s="2">
         <v>16</v>
       </c>
-      <c r="P32">
+      <c r="P32" s="2">
         <v>2</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2272,52 +2316,52 @@
       <c r="A33" s="1">
         <v>46170</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="4">
         <v>0.61527777777777781</v>
       </c>
       <c r="C33" t="s">
         <v>0</v>
       </c>
-      <c r="D33">
+      <c r="D33" s="2">
         <v>1433</v>
       </c>
       <c r="E33" t="s">
         <v>22</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2">
         <v>24</v>
       </c>
-      <c r="G33">
+      <c r="G33" s="2">
         <v>274</v>
       </c>
-      <c r="H33">
+      <c r="H33" s="3">
         <v>2.41</v>
       </c>
-      <c r="I33">
+      <c r="I33" s="2">
         <v>2756</v>
       </c>
       <c r="J33" t="s">
         <v>29</v>
       </c>
-      <c r="K33">
+      <c r="K33" s="2">
         <v>130</v>
       </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
+      <c r="L33" s="2">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2">
         <v>27</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
+      <c r="N33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2">
         <v>21</v>
       </c>
-      <c r="P33">
+      <c r="P33" s="2">
         <v>3</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2325,52 +2369,52 @@
       <c r="A34" s="1">
         <v>46171</v>
       </c>
-      <c r="B34" s="2">
+      <c r="B34" s="4">
         <v>0.56458333333333333</v>
       </c>
       <c r="C34" t="s">
         <v>0</v>
       </c>
-      <c r="D34">
+      <c r="D34" s="2">
         <v>4148</v>
       </c>
       <c r="E34" t="s">
         <v>22</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2">
         <v>57</v>
       </c>
-      <c r="G34">
+      <c r="G34" s="2">
         <v>757</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="3">
         <v>7.11</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="2">
         <v>8252</v>
       </c>
       <c r="J34" t="s">
         <v>27</v>
       </c>
-      <c r="K34">
+      <c r="K34" s="2">
         <v>124</v>
       </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
+      <c r="L34" s="2">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2">
         <v>67</v>
       </c>
-      <c r="N34">
+      <c r="N34" s="2">
         <v>3</v>
       </c>
-      <c r="O34">
+      <c r="O34" s="2">
         <v>66</v>
       </c>
-      <c r="P34">
+      <c r="P34" s="2">
         <v>1</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2378,52 +2422,52 @@
       <c r="A35" s="1">
         <v>46174</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="4">
         <v>0.55555555555555558</v>
       </c>
       <c r="C35" t="s">
         <v>0</v>
       </c>
-      <c r="D35">
+      <c r="D35" s="2">
         <v>3996</v>
       </c>
       <c r="E35" t="s">
         <v>22</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2">
         <v>61</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="2">
         <v>747</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="3">
         <v>5.68</v>
       </c>
-      <c r="I35">
+      <c r="I35" s="2">
         <v>7625</v>
       </c>
       <c r="J35" t="s">
         <v>14</v>
       </c>
-      <c r="K35">
+      <c r="K35" s="2">
         <v>124</v>
       </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35">
+      <c r="L35" s="2">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2">
         <v>71</v>
       </c>
-      <c r="N35">
+      <c r="N35" s="2">
         <v>1</v>
       </c>
-      <c r="O35">
+      <c r="O35" s="2">
         <v>55</v>
       </c>
-      <c r="P35">
+      <c r="P35" s="2">
         <v>8</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2431,52 +2475,52 @@
       <c r="A36" s="1">
         <v>46175</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="4">
         <v>0.54791666666666672</v>
       </c>
       <c r="C36" t="s">
         <v>0</v>
       </c>
-      <c r="D36">
+      <c r="D36" s="2">
         <v>3944</v>
       </c>
       <c r="E36" t="s">
         <v>22</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2">
         <v>74</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="2">
         <v>796</v>
       </c>
-      <c r="H36">
+      <c r="H36" s="3">
         <v>5.69</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="2">
         <v>7635</v>
       </c>
       <c r="J36" t="s">
         <v>23</v>
       </c>
-      <c r="K36">
+      <c r="K36" s="2">
         <v>132</v>
       </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
+      <c r="L36" s="2">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2">
         <v>69</v>
       </c>
-      <c r="N36">
+      <c r="N36" s="2">
         <v>2</v>
       </c>
-      <c r="O36">
+      <c r="O36" s="2">
         <v>27</v>
       </c>
-      <c r="P36">
+      <c r="P36" s="2">
         <v>15</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" s="2">
         <v>6</v>
       </c>
     </row>
@@ -2484,52 +2528,52 @@
       <c r="A37" s="1">
         <v>46176</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="4">
         <v>0.56041666666666667</v>
       </c>
       <c r="C37" t="s">
         <v>0</v>
       </c>
-      <c r="D37">
+      <c r="D37" s="2">
         <v>4154</v>
       </c>
       <c r="E37" t="s">
         <v>22</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2">
         <v>46</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="2">
         <v>709</v>
       </c>
-      <c r="H37">
+      <c r="H37" s="3">
         <v>5.75</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="2">
         <v>7842</v>
       </c>
       <c r="J37" t="s">
         <v>24</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="2">
         <v>118</v>
       </c>
-      <c r="L37">
-        <v>0</v>
-      </c>
-      <c r="M37">
+      <c r="L37" s="2">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2">
         <v>54</v>
       </c>
-      <c r="N37">
+      <c r="N37" s="2">
         <v>11</v>
       </c>
-      <c r="O37">
+      <c r="O37" s="2">
         <v>50</v>
       </c>
-      <c r="P37">
+      <c r="P37" s="2">
         <v>2</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2537,13 +2581,13 @@
       <c r="A38" s="1">
         <v>46176</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="4">
         <v>0.66666666666666663</v>
       </c>
       <c r="C38" t="s">
         <v>1</v>
       </c>
-      <c r="D38">
+      <c r="D38" s="2">
         <v>50</v>
       </c>
       <c r="E38" t="s">
@@ -2554,52 +2598,52 @@
       <c r="A39" s="1">
         <v>46177</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="4">
         <v>0.56388888888888888</v>
       </c>
       <c r="C39" t="s">
         <v>0</v>
       </c>
-      <c r="D39">
+      <c r="D39" s="2">
         <v>4300</v>
       </c>
       <c r="E39" t="s">
         <v>22</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2">
         <v>54</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="2">
         <v>763</v>
       </c>
-      <c r="H39">
+      <c r="H39" s="3">
         <v>5.76</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="2">
         <v>7904</v>
       </c>
       <c r="J39" t="s">
         <v>25</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="2">
         <v>124</v>
       </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
         <v>64</v>
       </c>
-      <c r="N39">
+      <c r="N39" s="2">
         <v>5</v>
       </c>
-      <c r="O39">
+      <c r="O39" s="2">
         <v>54</v>
       </c>
-      <c r="P39">
+      <c r="P39" s="2">
         <v>5</v>
       </c>
-      <c r="Q39">
+      <c r="Q39" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2607,13 +2651,13 @@
       <c r="A40" s="1">
         <v>46177</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="4">
         <v>0.52083333333333337</v>
       </c>
       <c r="C40" t="s">
         <v>2</v>
       </c>
-      <c r="D40">
+      <c r="D40" s="2">
         <v>60</v>
       </c>
       <c r="E40" t="s">
@@ -2624,13 +2668,13 @@
       <c r="A41" s="1">
         <v>46177</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="4">
         <v>0.6875</v>
       </c>
       <c r="C41" t="s">
         <v>1</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="2">
         <v>50</v>
       </c>
       <c r="E41" t="s">
@@ -2641,13 +2685,13 @@
       <c r="A42" s="1">
         <v>46179</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="4">
         <v>0.6875</v>
       </c>
       <c r="C42" t="s">
         <v>1</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="2">
         <v>50</v>
       </c>
       <c r="E42" t="s">
@@ -2658,13 +2702,13 @@
       <c r="A43" s="1">
         <v>46180</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="4">
         <v>0.85416666666666663</v>
       </c>
       <c r="C43" t="s">
         <v>1</v>
       </c>
-      <c r="D43">
+      <c r="D43" s="2">
         <v>50</v>
       </c>
       <c r="E43" t="s">
@@ -2675,13 +2719,13 @@
       <c r="A44" s="1">
         <v>46181</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="4">
         <v>8.3333333333333329E-2</v>
       </c>
       <c r="C44" t="s">
         <v>2</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="2">
         <v>60</v>
       </c>
       <c r="E44" t="s">
@@ -2692,13 +2736,13 @@
       <c r="A45" s="1">
         <v>46181</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="4">
         <v>0.5</v>
       </c>
       <c r="C45" t="s">
         <v>2</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="2">
         <v>60</v>
       </c>
       <c r="E45" t="s">
@@ -2709,52 +2753,52 @@
       <c r="A46" s="1">
         <v>46181</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="4">
         <v>0.56388888888888888</v>
       </c>
       <c r="C46" t="s">
         <v>0</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="2">
         <v>4297</v>
       </c>
       <c r="E46" t="s">
         <v>22</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="2">
         <v>28</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="2">
         <v>678</v>
       </c>
-      <c r="H46">
+      <c r="H46" s="3">
         <v>5.66</v>
       </c>
-      <c r="I46">
+      <c r="I46" s="2">
         <v>7793</v>
       </c>
       <c r="J46" t="s">
         <v>32</v>
       </c>
-      <c r="K46">
+      <c r="K46" s="2">
         <v>114</v>
       </c>
-      <c r="L46">
-        <v>0</v>
-      </c>
-      <c r="M46">
+      <c r="L46" s="2">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2">
         <v>29</v>
       </c>
-      <c r="N46">
+      <c r="N46" s="2">
         <v>27</v>
       </c>
-      <c r="O46">
+      <c r="O46" s="2">
         <v>25</v>
       </c>
-      <c r="P46">
+      <c r="P46" s="2">
         <v>2</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2762,13 +2806,13 @@
       <c r="A47" s="1">
         <v>46182</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="4">
         <v>0.50694444444444442</v>
       </c>
       <c r="C47" t="s">
         <v>1</v>
       </c>
-      <c r="D47">
+      <c r="D47" s="2">
         <v>50</v>
       </c>
       <c r="E47" t="s">
@@ -2779,13 +2823,13 @@
       <c r="A48" s="1">
         <v>46182</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="4">
         <v>0.51388888888888884</v>
       </c>
       <c r="C48" t="s">
         <v>2</v>
       </c>
-      <c r="D48">
+      <c r="D48" s="2">
         <v>60</v>
       </c>
       <c r="E48" t="s">
@@ -2796,52 +2840,52 @@
       <c r="A49" s="1">
         <v>46182</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="4">
         <v>0.58611111111111114</v>
       </c>
       <c r="C49" t="s">
         <v>0</v>
       </c>
-      <c r="D49">
+      <c r="D49" s="2">
         <v>4250</v>
       </c>
       <c r="E49" t="s">
         <v>22</v>
       </c>
-      <c r="F49">
+      <c r="F49" s="2">
         <v>36</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="2">
         <v>692</v>
       </c>
-      <c r="H49">
+      <c r="H49" s="3">
         <v>5.65</v>
       </c>
-      <c r="I49">
+      <c r="I49" s="2">
         <v>7785</v>
       </c>
       <c r="J49" t="s">
         <v>57</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="2">
         <v>117</v>
       </c>
-      <c r="L49">
-        <v>0</v>
-      </c>
-      <c r="M49">
+      <c r="L49" s="2">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2">
         <v>37</v>
       </c>
-      <c r="N49">
+      <c r="N49" s="2">
         <v>19</v>
       </c>
-      <c r="O49">
+      <c r="O49" s="2">
         <v>35</v>
       </c>
-      <c r="P49">
+      <c r="P49" s="2">
         <v>1</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2849,13 +2893,13 @@
       <c r="A50" s="1">
         <v>46182</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="4">
         <v>0.73611111111111116</v>
       </c>
       <c r="C50" t="s">
         <v>1</v>
       </c>
-      <c r="D50">
+      <c r="D50" s="2">
         <v>50</v>
       </c>
       <c r="E50" t="s">
@@ -2866,13 +2910,13 @@
       <c r="A51" s="1">
         <v>46182</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="4">
         <v>0.75</v>
       </c>
       <c r="C51" t="s">
         <v>2</v>
       </c>
-      <c r="D51">
+      <c r="D51" s="2">
         <v>60</v>
       </c>
       <c r="E51" t="s">
@@ -2883,13 +2927,13 @@
       <c r="A52" s="1">
         <v>46183</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="4">
         <v>0.45833333333333331</v>
       </c>
       <c r="C52" t="s">
         <v>2</v>
       </c>
-      <c r="D52">
+      <c r="D52" s="2">
         <v>60</v>
       </c>
       <c r="E52" t="s">
@@ -2900,52 +2944,52 @@
       <c r="A53" s="1">
         <v>46183</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="4">
         <v>0.47569444444444442</v>
       </c>
       <c r="C53" t="s">
         <v>0</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="2">
         <v>4046</v>
       </c>
       <c r="E53" t="s">
         <v>22</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="2">
         <v>38</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="2">
         <v>668</v>
       </c>
-      <c r="H53">
+      <c r="H53" s="3">
         <v>5.49</v>
       </c>
-      <c r="I53">
+      <c r="I53" s="2">
         <v>7519</v>
       </c>
       <c r="J53" t="s">
         <v>58</v>
       </c>
-      <c r="K53">
+      <c r="K53" s="2">
         <v>120</v>
       </c>
-      <c r="L53">
-        <v>0</v>
-      </c>
-      <c r="M53">
+      <c r="L53" s="2">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2">
         <v>48</v>
       </c>
-      <c r="N53">
+      <c r="N53" s="2">
         <v>10</v>
       </c>
-      <c r="O53">
+      <c r="O53" s="2">
         <v>40</v>
       </c>
-      <c r="P53">
+      <c r="P53" s="2">
         <v>4</v>
       </c>
-      <c r="Q53">
+      <c r="Q53" s="2">
         <v>0</v>
       </c>
     </row>
@@ -2953,69 +2997,69 @@
       <c r="A54" s="1">
         <v>46183</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="4">
         <v>0.79166666666666663</v>
       </c>
       <c r="C54" t="s">
         <v>1</v>
       </c>
-      <c r="D54">
+      <c r="D54" s="2">
         <v>50</v>
       </c>
       <c r="E54" t="s">
-        <v>60</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>46184</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="4">
         <v>0.40833333333333333</v>
       </c>
       <c r="C55" t="s">
         <v>0</v>
       </c>
-      <c r="D55">
+      <c r="D55" s="2">
         <v>3994</v>
       </c>
       <c r="E55" t="s">
         <v>22</v>
       </c>
-      <c r="F55">
+      <c r="F55" s="2">
         <v>40</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="2">
         <v>671</v>
       </c>
-      <c r="H55">
+      <c r="H55" s="3">
         <v>5.54</v>
       </c>
-      <c r="I55">
+      <c r="I55" s="2">
         <v>7633</v>
       </c>
       <c r="J55" t="s">
         <v>59</v>
       </c>
-      <c r="K55">
+      <c r="K55" s="2">
         <v>123</v>
       </c>
-      <c r="L55">
-        <v>0</v>
-      </c>
-      <c r="M55">
+      <c r="L55" s="2">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2">
         <v>44</v>
       </c>
-      <c r="N55">
+      <c r="N55" s="2">
         <v>9</v>
       </c>
-      <c r="O55">
+      <c r="O55" s="2">
         <v>44</v>
       </c>
-      <c r="P55">
-        <v>0</v>
-      </c>
-      <c r="Q55">
+      <c r="P55" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3023,13 +3067,13 @@
       <c r="A56" s="1">
         <v>46184</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="4">
         <v>0.66666666666666663</v>
       </c>
       <c r="C56" t="s">
         <v>1</v>
       </c>
-      <c r="D56">
+      <c r="D56" s="2">
         <v>50</v>
       </c>
       <c r="E56" t="s">
@@ -3040,13 +3084,13 @@
       <c r="A57" s="1">
         <v>46184</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="4">
         <v>0.77083333333333337</v>
       </c>
       <c r="C57" t="s">
         <v>1</v>
       </c>
-      <c r="D57">
+      <c r="D57" s="2">
         <v>50</v>
       </c>
       <c r="E57" t="s">
@@ -3057,13 +3101,13 @@
       <c r="A58" s="1">
         <v>46185</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="4">
         <v>0.45833333333333331</v>
       </c>
       <c r="C58" t="s">
         <v>1</v>
       </c>
-      <c r="D58">
+      <c r="D58" s="2">
         <v>50</v>
       </c>
       <c r="E58" t="s">
@@ -3074,13 +3118,13 @@
       <c r="A59" s="1">
         <v>46185</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="4">
         <v>0.52083333333333337</v>
       </c>
       <c r="C59" t="s">
         <v>2</v>
       </c>
-      <c r="D59">
+      <c r="D59" s="2">
         <v>60</v>
       </c>
       <c r="E59" t="s">
@@ -3091,52 +3135,52 @@
       <c r="A60" s="1">
         <v>46185</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="4">
         <v>0.53680555555555554</v>
       </c>
       <c r="C60" t="s">
         <v>0</v>
       </c>
-      <c r="D60">
+      <c r="D60" s="2">
         <v>3891</v>
       </c>
       <c r="E60" t="s">
         <v>22</v>
       </c>
-      <c r="F60">
+      <c r="F60" s="2">
         <v>38</v>
       </c>
-      <c r="G60">
+      <c r="G60" s="2">
         <v>678</v>
       </c>
-      <c r="H60">
+      <c r="H60" s="3">
         <v>5.5</v>
       </c>
-      <c r="I60">
+      <c r="I60" s="2">
         <v>7495</v>
       </c>
       <c r="J60" t="s">
-        <v>61</v>
-      </c>
-      <c r="K60">
+        <v>60</v>
+      </c>
+      <c r="K60" s="2">
         <v>124</v>
       </c>
-      <c r="L60">
-        <v>0</v>
-      </c>
-      <c r="M60">
+      <c r="L60" s="2">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2">
         <v>44</v>
       </c>
-      <c r="N60">
+      <c r="N60" s="2">
         <v>11</v>
       </c>
-      <c r="O60">
+      <c r="O60" s="2">
         <v>38</v>
       </c>
-      <c r="P60">
+      <c r="P60" s="2">
         <v>4</v>
       </c>
-      <c r="Q60">
+      <c r="Q60" s="2">
         <v>0</v>
       </c>
     </row>
@@ -3144,20 +3188,923 @@
       <c r="A61" s="1">
         <v>46186</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="4">
         <v>0.79166666666666663</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
       </c>
-      <c r="D61">
+      <c r="D61" s="2">
         <v>50</v>
       </c>
       <c r="E61" t="s">
         <v>3</v>
       </c>
     </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B62" s="4">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1</v>
+      </c>
+      <c r="D62" s="2">
+        <v>60</v>
+      </c>
+      <c r="E62" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B63" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1</v>
+      </c>
+      <c r="D63" s="2">
+        <v>60</v>
+      </c>
+      <c r="E63" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B64" s="4">
+        <v>0.39513888888888887</v>
+      </c>
+      <c r="C64" t="s">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2">
+        <v>4045</v>
+      </c>
+      <c r="E64" t="s">
+        <v>22</v>
+      </c>
+      <c r="F64" s="2">
+        <v>19</v>
+      </c>
+      <c r="G64" s="2">
+        <v>579</v>
+      </c>
+      <c r="H64" s="3">
+        <v>4.8499999999999996</v>
+      </c>
+      <c r="I64" s="2">
+        <v>6674</v>
+      </c>
+      <c r="J64" t="s">
+        <v>61</v>
+      </c>
+      <c r="K64" s="2">
+        <v>108</v>
+      </c>
+      <c r="L64" s="2">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2">
+        <v>21</v>
+      </c>
+      <c r="N64" s="2">
+        <v>13</v>
+      </c>
+      <c r="O64" s="2">
+        <v>23</v>
+      </c>
+      <c r="P64" s="2">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B65" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="2">
+        <v>60</v>
+      </c>
+      <c r="E65" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B66" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="2">
+        <v>60</v>
+      </c>
+      <c r="E66" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B67" s="4">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <v>60</v>
+      </c>
+      <c r="E67" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B68" s="4">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <v>60</v>
+      </c>
+      <c r="E68" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B69" s="4">
+        <v>0.47291666666666665</v>
+      </c>
+      <c r="C69" t="s">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2">
+        <v>3842</v>
+      </c>
+      <c r="E69" t="s">
+        <v>22</v>
+      </c>
+      <c r="F69" s="2">
+        <v>50</v>
+      </c>
+      <c r="G69" s="2">
+        <v>710</v>
+      </c>
+      <c r="H69" s="3">
+        <v>5.67</v>
+      </c>
+      <c r="I69" s="2">
+        <v>7501</v>
+      </c>
+      <c r="J69" t="s">
+        <v>62</v>
+      </c>
+      <c r="K69" s="2">
+        <v>138</v>
+      </c>
+      <c r="L69" s="2">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2">
+        <v>38</v>
+      </c>
+      <c r="N69" s="2">
+        <v>12</v>
+      </c>
+      <c r="O69" s="2">
+        <v>12</v>
+      </c>
+      <c r="P69" s="2">
+        <v>16</v>
+      </c>
+      <c r="Q69" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B70" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="2">
+        <v>60</v>
+      </c>
+      <c r="E70" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B71" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <v>60</v>
+      </c>
+      <c r="E71" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B72" s="4">
+        <v>0.45416666666666666</v>
+      </c>
+      <c r="C72" t="s">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2">
+        <v>3842</v>
+      </c>
+      <c r="E72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" s="2">
+        <v>52</v>
+      </c>
+      <c r="G72" s="2">
+        <v>690</v>
+      </c>
+      <c r="H72" s="3">
+        <v>5.46</v>
+      </c>
+      <c r="I72" s="2">
+        <v>7359</v>
+      </c>
+      <c r="J72" t="s">
+        <v>63</v>
+      </c>
+      <c r="K72" s="2">
+        <v>125</v>
+      </c>
+      <c r="L72" s="2">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2">
+        <v>60</v>
+      </c>
+      <c r="N72" s="2">
+        <v>3</v>
+      </c>
+      <c r="O72" s="2">
+        <v>52</v>
+      </c>
+      <c r="P72" s="2">
+        <v>4</v>
+      </c>
+      <c r="Q72" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B73" s="4">
+        <v>0.625</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="2">
+        <v>60</v>
+      </c>
+      <c r="E73" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B74" s="4">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <v>60</v>
+      </c>
+      <c r="E74" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B75" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="2">
+        <v>60</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>46192</v>
+      </c>
+      <c r="B76" s="4">
+        <v>0.52847222222222223</v>
+      </c>
+      <c r="C76" t="s">
+        <v>0</v>
+      </c>
+      <c r="D76" s="2">
+        <v>3894</v>
+      </c>
+      <c r="E76" t="s">
+        <v>22</v>
+      </c>
+      <c r="F76" s="2">
+        <v>62</v>
+      </c>
+      <c r="G76" s="2">
+        <v>731</v>
+      </c>
+      <c r="H76" s="3">
+        <v>5.61</v>
+      </c>
+      <c r="I76" s="2">
+        <v>7517</v>
+      </c>
+      <c r="J76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K76" s="2">
+        <v>130</v>
+      </c>
+      <c r="L76" s="2">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2">
+        <v>65</v>
+      </c>
+      <c r="N76" s="2">
+        <v>0</v>
+      </c>
+      <c r="O76" s="2">
+        <v>58</v>
+      </c>
+      <c r="P76" s="2">
+        <v>5</v>
+      </c>
+      <c r="Q76" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>46194</v>
+      </c>
+      <c r="B77" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="2">
+        <v>60</v>
+      </c>
+      <c r="E77" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B78" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="C78" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2">
+        <v>60</v>
+      </c>
+      <c r="E78" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B79" s="4">
+        <v>0.4465277777777778</v>
+      </c>
+      <c r="C79" t="s">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2">
+        <v>3840</v>
+      </c>
+      <c r="E79" t="s">
+        <v>22</v>
+      </c>
+      <c r="F79" s="2">
+        <v>64</v>
+      </c>
+      <c r="G79" s="2">
+        <v>746</v>
+      </c>
+      <c r="H79" s="3">
+        <v>5.72</v>
+      </c>
+      <c r="I79" s="2">
+        <v>7433</v>
+      </c>
+      <c r="J79" t="s">
+        <v>65</v>
+      </c>
+      <c r="K79" s="2">
+        <v>139</v>
+      </c>
+      <c r="L79" s="2">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2">
+        <v>64</v>
+      </c>
+      <c r="N79" s="2">
+        <v>8</v>
+      </c>
+      <c r="O79" s="2">
+        <v>22</v>
+      </c>
+      <c r="P79" s="2">
+        <v>23</v>
+      </c>
+      <c r="Q79" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B80" s="4">
+        <v>0.5625</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="2">
+        <v>60</v>
+      </c>
+      <c r="E80" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B81" s="4">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="C81" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2">
+        <v>60</v>
+      </c>
+      <c r="E81" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B82" s="4">
+        <v>0.6479166666666667</v>
+      </c>
+      <c r="C82" t="s">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2">
+        <v>2304</v>
+      </c>
+      <c r="E82" t="s">
+        <v>22</v>
+      </c>
+      <c r="F82" s="2">
+        <v>41</v>
+      </c>
+      <c r="G82" s="2">
+        <v>431</v>
+      </c>
+      <c r="H82" s="3">
+        <v>2.82</v>
+      </c>
+      <c r="I82" s="2">
+        <v>3871</v>
+      </c>
+      <c r="J82" t="s">
+        <v>66</v>
+      </c>
+      <c r="K82" s="2">
+        <v>128</v>
+      </c>
+      <c r="L82" s="2">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2">
+        <v>38</v>
+      </c>
+      <c r="N82" s="2">
+        <v>3</v>
+      </c>
+      <c r="O82" s="2">
+        <v>24</v>
+      </c>
+      <c r="P82" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q82" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B83" s="4">
+        <v>0.6875</v>
+      </c>
+      <c r="C83" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2">
+        <v>60</v>
+      </c>
+      <c r="E83" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B84" s="4">
+        <v>0.8125</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="2">
+        <v>60</v>
+      </c>
+      <c r="E84" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B85" s="4">
+        <v>0.46111111111111114</v>
+      </c>
+      <c r="C85" t="s">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2">
+        <v>3687</v>
+      </c>
+      <c r="E85" t="s">
+        <v>22</v>
+      </c>
+      <c r="F85" s="2">
+        <v>19</v>
+      </c>
+      <c r="G85" s="2">
+        <v>618</v>
+      </c>
+      <c r="H85" s="3">
+        <v>5.72</v>
+      </c>
+      <c r="I85" s="2">
+        <v>7279</v>
+      </c>
+      <c r="J85" t="s">
+        <v>67</v>
+      </c>
+      <c r="K85" s="2">
+        <v>118</v>
+      </c>
+      <c r="L85" s="2">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2">
+        <v>19</v>
+      </c>
+      <c r="N85" s="2">
+        <v>10</v>
+      </c>
+      <c r="O85" s="2">
+        <v>23</v>
+      </c>
+      <c r="P85" s="2">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B86" s="4">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="2">
+        <v>60</v>
+      </c>
+      <c r="E86" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B87" s="4">
+        <v>0.4375</v>
+      </c>
+      <c r="C87" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2">
+        <v>60</v>
+      </c>
+      <c r="E87" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B88" s="4">
+        <v>0.44583333333333336</v>
+      </c>
+      <c r="C88" t="s">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2">
+        <v>3840</v>
+      </c>
+      <c r="E88" t="s">
+        <v>22</v>
+      </c>
+      <c r="F88" s="2">
+        <v>66</v>
+      </c>
+      <c r="G88" s="2">
+        <v>749</v>
+      </c>
+      <c r="H88" s="3">
+        <v>5.26</v>
+      </c>
+      <c r="I88" s="2">
+        <v>7239</v>
+      </c>
+      <c r="J88" t="s">
+        <v>53</v>
+      </c>
+      <c r="K88" s="2">
+        <v>133</v>
+      </c>
+      <c r="L88" s="2">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2">
+        <v>77</v>
+      </c>
+      <c r="N88" s="2">
+        <v>1</v>
+      </c>
+      <c r="O88" s="2">
+        <v>28</v>
+      </c>
+      <c r="P88" s="2">
+        <v>27</v>
+      </c>
+      <c r="Q88" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B89" s="4">
+        <v>0.5625</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="2">
+        <v>60</v>
+      </c>
+      <c r="E89" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B90" s="4">
+        <v>0.9375</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="2">
+        <v>60</v>
+      </c>
+      <c r="E90" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B91" s="4">
+        <v>0.48680555555555555</v>
+      </c>
+      <c r="C91" t="s">
+        <v>0</v>
+      </c>
+      <c r="D91" s="2">
+        <v>3738</v>
+      </c>
+      <c r="E91" t="s">
+        <v>22</v>
+      </c>
+      <c r="F91" s="2">
+        <v>46</v>
+      </c>
+      <c r="G91" s="2">
+        <v>699</v>
+      </c>
+      <c r="H91" s="3">
+        <v>5.49</v>
+      </c>
+      <c r="I91" s="2">
+        <v>7278</v>
+      </c>
+      <c r="J91" t="s">
+        <v>73</v>
+      </c>
+      <c r="K91" s="2">
+        <v>124</v>
+      </c>
+      <c r="L91" s="2">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2">
+        <v>57</v>
+      </c>
+      <c r="N91" s="2">
+        <v>6</v>
+      </c>
+      <c r="O91" s="2">
+        <v>34</v>
+      </c>
+      <c r="P91" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q91" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B92" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="2">
+        <v>60</v>
+      </c>
+      <c r="E92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B93" s="4">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="C93" t="s">
+        <v>1</v>
+      </c>
+      <c r="D93" s="2">
+        <v>60</v>
+      </c>
+      <c r="E93" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>46200</v>
+      </c>
+      <c r="B94" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="2">
+        <v>60</v>
+      </c>
+      <c r="E94" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>46201</v>
+      </c>
+      <c r="B95" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="C95" t="s">
+        <v>1</v>
+      </c>
+      <c r="D95" s="2">
+        <v>60</v>
+      </c>
+      <c r="E95" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:Q92" xr:uid="{F196B904-6553-42BC-A222-B01279AC4ED1}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>